--- a/Test Cases Report/TestCases_PetStore.xlsx
+++ b/Test Cases Report/TestCases_PetStore.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SWD_depi\Technical\Projects\API\Pet Store Website Project\Test Cases Report\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BB31F3-1533-452E-B68C-0DE277472B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="الورقة1" sheetId="1" r:id="rId4"/>
+    <sheet name="الورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="411">
   <si>
     <t>Team Name</t>
   </si>
@@ -498,41 +507,1341 @@
   </si>
   <si>
     <t>❌ Returns 404</t>
+  </si>
+  <si>
+    <t>SC_INV_01</t>
+  </si>
+  <si>
+    <t>ST_INV_01</t>
+  </si>
+  <si>
+    <t>Valid inventory fetch</t>
+  </si>
+  <si>
+    <t>Ensure inventory list returns successfully</t>
+  </si>
+  <si>
+    <t>API is reachable</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Send GET request to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/inventory</t>
+    </r>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>HTTP 200 with inventory details</t>
+  </si>
+  <si>
+    <t>As expected</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>SC_INV_02</t>
+  </si>
+  <si>
+    <t>ST_INV_02</t>
+  </si>
+  <si>
+    <t>Validate inventory structure</t>
+  </si>
+  <si>
+    <t>Validate presence of expected inventory keys</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Keys like </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>available</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> present</t>
+    </r>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>SC_INV_03</t>
+  </si>
+  <si>
+    <t>ST_INV_03</t>
+  </si>
+  <si>
+    <t>Validate response format</t>
+  </si>
+  <si>
+    <t>Ensure response is returned in JSON</t>
+  </si>
+  <si>
+    <r>
+      <t>application/json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in headers</t>
+    </r>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Send GET to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/inventory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Inspect JSON keys</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/inventory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Check Content-Type header</t>
+    </r>
+  </si>
+  <si>
+    <t>Store_INV</t>
+  </si>
+  <si>
+    <t>SC_ORD_01</t>
+  </si>
+  <si>
+    <t>ST_ORD_01</t>
+  </si>
+  <si>
+    <t>Create valid order</t>
+  </si>
+  <si>
+    <t>Validate placing an order with correct fields</t>
+  </si>
+  <si>
+    <t>API is available</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. POST to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/order</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with full payload</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "petId": 1, "quantity": 2 }</t>
+  </si>
+  <si>
+    <t>HTTP 200 OK with orderId</t>
+  </si>
+  <si>
+    <t>SC_ORD_02</t>
+  </si>
+  <si>
+    <t>ST_ORD_02</t>
+  </si>
+  <si>
+    <t>Missing petId field</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Attempt order without required </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>petId</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. POST to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/order</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> without </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>petId</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "quantity": 2 }</t>
+  </si>
+  <si>
+    <t>400 Bad Request</t>
+  </si>
+  <si>
+    <t>SC_ORD_03</t>
+  </si>
+  <si>
+    <t>ST_ORD_03</t>
+  </si>
+  <si>
+    <t>Negative quantity allowed</t>
+  </si>
+  <si>
+    <t>Validate negative quantity is rejected</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. POST to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/order</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>quantity: -5</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "petId": 1, "quantity": -5 }</t>
+  </si>
+  <si>
+    <t>Order created (BUG)</t>
+  </si>
+  <si>
+    <t>Store_ORD</t>
+  </si>
+  <si>
+    <t>SC_ORD_ID_01</t>
+  </si>
+  <si>
+    <t>ST_ORD_ID_01</t>
+  </si>
+  <si>
+    <t>Get valid order</t>
+  </si>
+  <si>
+    <t>Retrieve order using valid ID</t>
+  </si>
+  <si>
+    <t>Known valid order exists</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/order/1</t>
+    </r>
+  </si>
+  <si>
+    <t>orderId = 1</t>
+  </si>
+  <si>
+    <t>200 OK with order data</t>
+  </si>
+  <si>
+    <t>SC_ORD_ID_02</t>
+  </si>
+  <si>
+    <t>ST_ORD_ID_02</t>
+  </si>
+  <si>
+    <t>Get non-existent order</t>
+  </si>
+  <si>
+    <t>Use non-existing orderId</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/order/99999</t>
+    </r>
+  </si>
+  <si>
+    <t>orderId = 99999</t>
+  </si>
+  <si>
+    <t>404 Not Found</t>
+  </si>
+  <si>
+    <t>SC_ORD_ID_03</t>
+  </si>
+  <si>
+    <t>ST_ORD_ID_03</t>
+  </si>
+  <si>
+    <t>Invalid orderId format</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/order/abc</t>
+    </r>
+  </si>
+  <si>
+    <t>orderId = abc</t>
+  </si>
+  <si>
+    <t>404 returned (BUG)</t>
+  </si>
+  <si>
+    <t>Store_ORD_ID</t>
+  </si>
+  <si>
+    <t>SC_DEL_01</t>
+  </si>
+  <si>
+    <t>ST_DEL_01</t>
+  </si>
+  <si>
+    <t>Delete valid order</t>
+  </si>
+  <si>
+    <t>Delete an order by ID</t>
+  </si>
+  <si>
+    <t>Order must exist</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. DELETE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/order/1</t>
+    </r>
+  </si>
+  <si>
+    <t>200 OK</t>
+  </si>
+  <si>
+    <t>SC_DEL_02</t>
+  </si>
+  <si>
+    <t>ST_DEL_02</t>
+  </si>
+  <si>
+    <t>Delete non-existing order</t>
+  </si>
+  <si>
+    <t>Try deleting non-existent order</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. DELETE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/order/99999</t>
+    </r>
+  </si>
+  <si>
+    <t>SC_DEL_03</t>
+  </si>
+  <si>
+    <t>ST_DEL_03</t>
+  </si>
+  <si>
+    <t>Invalid order ID</t>
+  </si>
+  <si>
+    <t>Use invalid orderId format</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. DELETE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/store/order/test</t>
+    </r>
+  </si>
+  <si>
+    <t>orderId = test</t>
+  </si>
+  <si>
+    <t>Store_DEL</t>
+  </si>
+  <si>
+    <t>SC_USER_01</t>
+  </si>
+  <si>
+    <t>US01</t>
+  </si>
+  <si>
+    <t>Create valid user</t>
+  </si>
+  <si>
+    <t>Create user with valid data</t>
+  </si>
+  <si>
+    <t>API up</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. POST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with full payload</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "username": "john", "email": "john@example.com" }</t>
+  </si>
+  <si>
+    <t>HTTP 200 OK</t>
+  </si>
+  <si>
+    <t>SC_USER_02</t>
+  </si>
+  <si>
+    <t>US02</t>
+  </si>
+  <si>
+    <t>Missing username</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create user without </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>username</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. POST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> without </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>username</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "email": "john@example.com" }</t>
+  </si>
+  <si>
+    <t>200 OK (BUG)</t>
+  </si>
+  <si>
+    <t>SC_USER_03</t>
+  </si>
+  <si>
+    <t>US03</t>
+  </si>
+  <si>
+    <t>Invalid email format</t>
+  </si>
+  <si>
+    <t>Use incorrect email format</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. POST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>email: "bad"</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "username": "john", "email": "bad" }</t>
+  </si>
+  <si>
+    <t>Create_Single_User</t>
+  </si>
+  <si>
+    <t>SC_USER_04</t>
+  </si>
+  <si>
+    <t>US04</t>
+  </si>
+  <si>
+    <t>Create user list</t>
+  </si>
+  <si>
+    <t>Create multiple users via list</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. POST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/createWithList</t>
+    </r>
+  </si>
+  <si>
+    <t>[{"username": "user1"}, {"username": "user2"}]</t>
+  </si>
+  <si>
+    <t>SC_USER_05</t>
+  </si>
+  <si>
+    <t>US05</t>
+  </si>
+  <si>
+    <t>Empty user list</t>
+  </si>
+  <si>
+    <t>Send an empty array</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>HTTP 200 OK or warning</t>
+  </si>
+  <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>SC_USER_06</t>
+  </si>
+  <si>
+    <t>US06</t>
+  </si>
+  <si>
+    <t>Invalid list entry</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">One entry missing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>username</t>
+    </r>
+  </si>
+  <si>
+    <t>[{"username": "user1"}, {"email": "no_username"}]</t>
+  </si>
+  <si>
+    <t>Create_with_list</t>
+  </si>
+  <si>
+    <t>SC_USER_07</t>
+  </si>
+  <si>
+    <t>US07</t>
+  </si>
+  <si>
+    <t>Create user array</t>
+  </si>
+  <si>
+    <t>Create multiple users via array</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. POST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/createWithArray</t>
+    </r>
+  </si>
+  <si>
+    <t>[{"username": "userA"}, {"username": "userB"}]</t>
+  </si>
+  <si>
+    <t>SC_USER_08</t>
+  </si>
+  <si>
+    <t>US08</t>
+  </si>
+  <si>
+    <t>Malformed JSON</t>
+  </si>
+  <si>
+    <t>Send badly formatted array</t>
+  </si>
+  <si>
+    <t>[{"username": "user1"</t>
+  </si>
+  <si>
+    <t>HTTP 400 Bad Request</t>
+  </si>
+  <si>
+    <t>SC_USER_09</t>
+  </si>
+  <si>
+    <t>US09</t>
+  </si>
+  <si>
+    <t>Duplicates in array</t>
+  </si>
+  <si>
+    <t>Include duplicate usernames</t>
+  </si>
+  <si>
+    <t>[{"username": "dup"}, {"username": "dup"}]</t>
+  </si>
+  <si>
+    <t>Either reject or allow based on backend rules</t>
+  </si>
+  <si>
+    <t>Create_with_array</t>
+  </si>
+  <si>
+    <t>SC_USER_10</t>
+  </si>
+  <si>
+    <t>US10</t>
+  </si>
+  <si>
+    <t>Get existing user</t>
+  </si>
+  <si>
+    <t>Fetch details of a valid user</t>
+  </si>
+  <si>
+    <t>User exists</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/john</t>
+    </r>
+  </si>
+  <si>
+    <t>username = john</t>
+  </si>
+  <si>
+    <t>HTTP 200 with user data</t>
+  </si>
+  <si>
+    <t>SC_USER_11</t>
+  </si>
+  <si>
+    <t>US11</t>
+  </si>
+  <si>
+    <t>Non-existing user</t>
+  </si>
+  <si>
+    <t>Try to get user not in system</t>
+  </si>
+  <si>
+    <t>User does not exist</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/ghost</t>
+    </r>
+  </si>
+  <si>
+    <t>username = ghost</t>
+  </si>
+  <si>
+    <t>HTTP 404 Not Found</t>
+  </si>
+  <si>
+    <t>SC_USER_12</t>
+  </si>
+  <si>
+    <t>US12</t>
+  </si>
+  <si>
+    <t>Blank username</t>
+  </si>
+  <si>
+    <t>Use empty path param</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/</t>
+    </r>
+  </si>
+  <si>
+    <t>username = blank</t>
+  </si>
+  <si>
+    <t>HTTP 405 or 400</t>
+  </si>
+  <si>
+    <t>User_Username</t>
+  </si>
+  <si>
+    <t>SC_USER_13</t>
+  </si>
+  <si>
+    <t>US13</t>
+  </si>
+  <si>
+    <t>Update valid user</t>
+  </si>
+  <si>
+    <t>Update existing user info</t>
+  </si>
+  <si>
+    <t>User must exist</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. PUT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/john</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with body</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "email": "updated@example.com" }</t>
+  </si>
+  <si>
+    <t>SC_USER_14</t>
+  </si>
+  <si>
+    <t>US14</t>
+  </si>
+  <si>
+    <t>Update non-existing user</t>
+  </si>
+  <si>
+    <t>Attempt update on unknown user</t>
+  </si>
+  <si>
+    <t>User doesn't exist</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PUT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/ghost</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "email": "test@example.com" }</t>
+  </si>
+  <si>
+    <t>HTTP 404 or error</t>
+  </si>
+  <si>
+    <t>SC_USER_15</t>
+  </si>
+  <si>
+    <t>US15</t>
+  </si>
+  <si>
+    <t>Invalid update format</t>
+  </si>
+  <si>
+    <t>Send invalid JSON</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PUT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/john</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with malformed JSON</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "email": "bad</t>
+  </si>
+  <si>
+    <t>SC_USER_16</t>
+  </si>
+  <si>
+    <t>US16</t>
+  </si>
+  <si>
+    <t>Delete valid user</t>
+  </si>
+  <si>
+    <t>Delete an existing user</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DELETE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/john</t>
+    </r>
+  </si>
+  <si>
+    <t>SC_USER_17</t>
+  </si>
+  <si>
+    <t>US17</t>
+  </si>
+  <si>
+    <t>Delete non-existent user</t>
+  </si>
+  <si>
+    <t>Try to delete a ghost user</t>
+  </si>
+  <si>
+    <t>User not in DB</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DELETE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/ghost</t>
+    </r>
+  </si>
+  <si>
+    <t>SC_USER_18</t>
+  </si>
+  <si>
+    <t>US18</t>
+  </si>
+  <si>
+    <t>Blank username in delete</t>
+  </si>
+  <si>
+    <t>Leave path parameter empty</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DELETE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/</t>
+    </r>
+  </si>
+  <si>
+    <t>blank</t>
+  </si>
+  <si>
+    <t>HTTP 400 or 405</t>
+  </si>
+  <si>
+    <t>User_Del</t>
+  </si>
+  <si>
+    <t>SC_USER_19</t>
+  </si>
+  <si>
+    <t>US19</t>
+  </si>
+  <si>
+    <t>Valid login</t>
+  </si>
+  <si>
+    <t>Login with correct credentials</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/login?username=john&amp;password=1234</t>
+    </r>
+  </si>
+  <si>
+    <t>valid creds</t>
+  </si>
+  <si>
+    <t>HTTP 200 + session token</t>
+  </si>
+  <si>
+    <t>SC_USER_20</t>
+  </si>
+  <si>
+    <t>US20</t>
+  </si>
+  <si>
+    <t>Invalid password</t>
+  </si>
+  <si>
+    <t>Wrong password provided</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/login?username=john&amp;password=wrong</t>
+    </r>
+  </si>
+  <si>
+    <t>wrong password</t>
+  </si>
+  <si>
+    <t>SC_USER_21</t>
+  </si>
+  <si>
+    <t>US21</t>
+  </si>
+  <si>
+    <t>Send empty username</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/login?username=&amp;password=1234</t>
+    </r>
+  </si>
+  <si>
+    <t>missing username</t>
+  </si>
+  <si>
+    <t>User_Login</t>
+  </si>
+  <si>
+    <t>SC_USER_22</t>
+  </si>
+  <si>
+    <t>US22</t>
+  </si>
+  <si>
+    <t>Logout after login</t>
+  </si>
+  <si>
+    <t>Logs out a logged-in user</t>
+  </si>
+  <si>
+    <t>User logged in</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/logout</t>
+    </r>
+  </si>
+  <si>
+    <t>SC_USER_23</t>
+  </si>
+  <si>
+    <t>US23</t>
+  </si>
+  <si>
+    <t>Logout without login</t>
+  </si>
+  <si>
+    <t>Logout without active session</t>
+  </si>
+  <si>
+    <t>Still returns 200 OK (stateless)</t>
+  </si>
+  <si>
+    <t>SC_USER_24</t>
+  </si>
+  <si>
+    <t>US24</t>
+  </si>
+  <si>
+    <t>Multiple logouts</t>
+  </si>
+  <si>
+    <t>Repeated logout calls</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/user/logout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> twice</t>
+    </r>
+  </si>
+  <si>
+    <t>Both return HTTP 200</t>
+  </si>
+  <si>
+    <t>User_Logout</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -564,41 +1873,20 @@
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
-    <border/>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -607,61 +1895,116 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -851,866 +2194,2292 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M59"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.5"/>
-    <col customWidth="1" min="2" max="2" width="19.5"/>
-    <col customWidth="1" min="3" max="3" width="10.0"/>
-    <col customWidth="1" min="4" max="4" width="33.0"/>
-    <col customWidth="1" min="5" max="5" width="39.88"/>
-    <col customWidth="1" min="6" max="6" width="31.38"/>
-    <col customWidth="1" min="7" max="7" width="32.0"/>
-    <col customWidth="1" min="8" max="8" width="22.0"/>
-    <col customWidth="1" min="9" max="9" width="33.75"/>
-    <col customWidth="1" min="10" max="10" width="32.0"/>
+    <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="33" customWidth="1"/>
+    <col min="5" max="5" width="39.88671875" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="38" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="33.77734375" customWidth="1"/>
+    <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7">
-        <v>45744.0</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="s">
+      <c r="B4" s="10">
+        <v>45744</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="54.75" customHeight="1">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:13" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="54.0" customHeight="1">
-      <c r="A7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="9" t="s">
+    <row r="7" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" ht="63.75" customHeight="1">
-      <c r="A8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="9" t="s">
+    <row r="8" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" ht="66.0" customHeight="1">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="9">
-        <v>123456.0</v>
-      </c>
-      <c r="I9" s="9" t="s">
+      <c r="H9" s="4">
+        <v>123456</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="69.0" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="1:13" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14"/>
+      <c r="B10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="9">
-        <v>9.9999999E7</v>
-      </c>
-      <c r="I10" s="9" t="s">
+      <c r="H10" s="4">
+        <v>99999999</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" ht="63.75" customHeight="1">
-      <c r="A11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="9" t="s">
+    <row r="11" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14"/>
+      <c r="B11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="M11" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" ht="68.25" customHeight="1">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" ht="69.0" customHeight="1">
-      <c r="A13" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="9" t="s">
+    <row r="13" spans="1:13" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
+      <c r="B13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" ht="73.5" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="9" t="s">
+    <row r="14" spans="1:13" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14"/>
+      <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="M14" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="56.25" customHeight="1">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:13" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" ht="55.5" customHeight="1">
-      <c r="A16" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="9" t="s">
+    <row r="16" spans="1:13" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14"/>
+      <c r="B16" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="L16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="M16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" ht="74.25" customHeight="1">
-      <c r="A17" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="9" t="s">
+    <row r="17" spans="1:13" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14"/>
+      <c r="B17" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="M17" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="18" ht="54.75" customHeight="1">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:13" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="M18" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" ht="45.75" customHeight="1">
-      <c r="A19" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" s="9" t="s">
+    <row r="19" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14"/>
+      <c r="B19" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="L19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="M19" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" ht="58.5" customHeight="1">
-      <c r="A20" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="9" t="s">
+    <row r="20" spans="1:13" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+      <c r="B20" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="M20" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21" ht="47.25" customHeight="1">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="H21" s="9">
-        <v>123456.0</v>
-      </c>
-      <c r="I21" s="9" t="s">
+      <c r="H21" s="4">
+        <v>123456</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="M21" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" ht="46.5" customHeight="1">
-      <c r="A22" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14"/>
+      <c r="B22" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H22" s="9">
-        <v>9.9999999E7</v>
-      </c>
-      <c r="I22" s="9" t="s">
+      <c r="H22" s="4">
+        <v>99999999</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="M22" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="23" ht="39.0" customHeight="1">
-      <c r="A23" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="9" t="s">
+    <row r="23" spans="1:13" s="18" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14"/>
+      <c r="B23" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="9" t="s">
+      <c r="M23" s="17" t="s">
         <v>42</v>
       </c>
     </row>
+    <row r="24" spans="1:13" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="70.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="15"/>
+      <c r="B26" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="70.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="73.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="15"/>
+      <c r="B31" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="76.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="79.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="79.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="82.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="100.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="73.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="15"/>
+      <c r="B37" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="88.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="15"/>
+      <c r="B38" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="91.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="15"/>
+      <c r="B40" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="100.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="15"/>
+      <c r="B41" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="79.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="15"/>
+      <c r="B43" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15"/>
+      <c r="B44" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="15"/>
+      <c r="B46" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="15"/>
+      <c r="B47" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="15"/>
+      <c r="B49" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="15"/>
+      <c r="B50" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="103.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="15"/>
+      <c r="B52" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="83.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="15"/>
+      <c r="B53" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="15"/>
+      <c r="B55" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="15"/>
+      <c r="B56" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="97.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="15"/>
+      <c r="B58" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="15"/>
+      <c r="B59" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="22">
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A20"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B4:G4"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>